--- a/Result/checksun_type/電子紙.xlsx
+++ b/Result/checksun_type/電子紙.xlsx
@@ -641,62 +641,62 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>my_signal</t>
+          <t>up_up</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_3d</t>
+          <t>up_up_3d</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_5d</t>
+          <t>up_up_5d</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_10d</t>
+          <t>up_up_10d</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>up_up</t>
+          <t>bbw_cross</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>up_up_3d</t>
+          <t>MA_UP_d</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>up_up_5d</t>
+          <t>MA_UP_3d</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>up_up_10d</t>
+          <t>MA_UP_5d</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>bbw_cross</t>
+          <t>MA_UP_10d</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_3d</t>
+          <t>MA_UP_20d</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_5d</t>
+          <t>MA_UP_30d</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_10d</t>
+          <t>MA_UP_40d</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -1893,11 +1893,15 @@
           <t>144.55</t>
         </is>
       </c>
-      <c r="CQ2" t="n">
-        <v>146.02</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>161.98</v>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>146.02</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>161.98</t>
+        </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
@@ -2650,7 +2654,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -2665,7 +2669,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -2875,11 +2879,15 @@
           <t>145.0</t>
         </is>
       </c>
-      <c r="CQ3" t="n">
-        <v>146.57</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>163</v>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>146.57</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>163.0</t>
+        </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
@@ -3632,7 +3640,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -3647,7 +3655,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -3857,11 +3865,15 @@
           <t>145.2</t>
         </is>
       </c>
-      <c r="CQ4" t="n">
-        <v>147.28</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>163.98</v>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>147.28</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>163.98</t>
+        </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
@@ -4614,7 +4626,7 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -4629,7 +4641,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -4839,11 +4851,15 @@
           <t>145.35</t>
         </is>
       </c>
-      <c r="CQ5" t="n">
-        <v>147.9</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>164.61</v>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>147.9</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>164.61</t>
+        </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
@@ -5596,7 +5612,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -5611,7 +5627,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -5821,11 +5837,15 @@
           <t>145.7</t>
         </is>
       </c>
-      <c r="CQ6" t="n">
-        <v>148.8</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>165.39</v>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>148.8</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>165.39</t>
+        </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
@@ -6578,7 +6598,7 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -6593,7 +6613,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -6803,11 +6823,15 @@
           <t>145.8</t>
         </is>
       </c>
-      <c r="CQ7" t="n">
-        <v>149.45</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>166.15</v>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>149.45</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>166.15</t>
+        </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
@@ -7560,7 +7584,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -7575,7 +7599,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -7785,11 +7809,15 @@
           <t>146.35</t>
         </is>
       </c>
-      <c r="CQ8" t="n">
-        <v>150.25</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>167.04</v>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>150.25</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>167.04</t>
+        </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
@@ -8542,7 +8570,7 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -8557,7 +8585,7 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
@@ -8767,11 +8795,15 @@
           <t>146.55</t>
         </is>
       </c>
-      <c r="CQ9" t="n">
-        <v>150.93</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>168.01</v>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>150.93</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>168.01</t>
+        </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
@@ -9524,7 +9556,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -9539,7 +9571,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
@@ -9749,11 +9781,15 @@
           <t>147.15</t>
         </is>
       </c>
-      <c r="CQ10" t="n">
-        <v>151.62</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>169.04</v>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>151.62</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>169.04</t>
+        </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
@@ -10506,7 +10542,7 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
@@ -10521,7 +10557,7 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
@@ -10531,12 +10567,12 @@
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -10731,11 +10767,15 @@
           <t>81.6</t>
         </is>
       </c>
-      <c r="CQ11" t="n">
-        <v>82.66</v>
-      </c>
-      <c r="CR11" t="n">
-        <v>87.06</v>
+      <c r="CQ11" t="inlineStr">
+        <is>
+          <t>82.66</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>87.06</t>
+        </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
@@ -11488,7 +11528,7 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
@@ -11503,7 +11543,7 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
@@ -11513,12 +11553,12 @@
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -11713,11 +11753,15 @@
           <t>81.76</t>
         </is>
       </c>
-      <c r="CQ12" t="n">
-        <v>83.05</v>
-      </c>
-      <c r="CR12" t="n">
-        <v>87.39</v>
+      <c r="CQ12" t="inlineStr">
+        <is>
+          <t>83.05</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
+          <t>87.39</t>
+        </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
@@ -12470,7 +12514,7 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
@@ -12485,7 +12529,7 @@
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
@@ -12495,12 +12539,12 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -12695,11 +12739,15 @@
           <t>81.83</t>
         </is>
       </c>
-      <c r="CQ13" t="n">
-        <v>83.44</v>
-      </c>
-      <c r="CR13" t="n">
-        <v>87.7</v>
+      <c r="CQ13" t="inlineStr">
+        <is>
+          <t>83.44</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
+          <t>87.7</t>
+        </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
@@ -13452,7 +13500,7 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
@@ -13467,7 +13515,7 @@
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
@@ -13477,12 +13525,12 @@
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
@@ -13677,11 +13725,15 @@
           <t>81.75</t>
         </is>
       </c>
-      <c r="CQ14" t="n">
-        <v>83.81999999999999</v>
-      </c>
-      <c r="CR14" t="n">
-        <v>87.98999999999999</v>
+      <c r="CQ14" t="inlineStr">
+        <is>
+          <t>83.82</t>
+        </is>
+      </c>
+      <c r="CR14" t="inlineStr">
+        <is>
+          <t>87.99</t>
+        </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
@@ -14434,7 +14486,7 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
@@ -14449,7 +14501,7 @@
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
@@ -14459,12 +14511,12 @@
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -14659,11 +14711,15 @@
           <t>81.74</t>
         </is>
       </c>
-      <c r="CQ15" t="n">
-        <v>84.23999999999999</v>
-      </c>
-      <c r="CR15" t="n">
-        <v>88.34999999999999</v>
+      <c r="CQ15" t="inlineStr">
+        <is>
+          <t>84.24</t>
+        </is>
+      </c>
+      <c r="CR15" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
@@ -15416,7 +15472,7 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
@@ -15431,7 +15487,7 @@
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
@@ -15441,12 +15497,12 @@
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -15641,11 +15697,15 @@
           <t>81.84</t>
         </is>
       </c>
-      <c r="CQ16" t="n">
-        <v>84.67</v>
-      </c>
-      <c r="CR16" t="n">
-        <v>88.79000000000001</v>
+      <c r="CQ16" t="inlineStr">
+        <is>
+          <t>84.67</t>
+        </is>
+      </c>
+      <c r="CR16" t="inlineStr">
+        <is>
+          <t>88.79</t>
+        </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
@@ -16398,7 +16458,7 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
@@ -16413,7 +16473,7 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
@@ -16423,12 +16483,12 @@
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -16623,11 +16683,15 @@
           <t>82.08</t>
         </is>
       </c>
-      <c r="CQ17" t="n">
-        <v>85.13</v>
-      </c>
-      <c r="CR17" t="n">
-        <v>89.23</v>
+      <c r="CQ17" t="inlineStr">
+        <is>
+          <t>85.13</t>
+        </is>
+      </c>
+      <c r="CR17" t="inlineStr">
+        <is>
+          <t>89.23</t>
+        </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
@@ -17380,7 +17444,7 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
@@ -17395,22 +17459,22 @@
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -17605,11 +17669,15 @@
           <t>82.30999999999999</t>
         </is>
       </c>
-      <c r="CQ18" t="n">
-        <v>85.48999999999999</v>
-      </c>
-      <c r="CR18" t="n">
-        <v>89.58</v>
+      <c r="CQ18" t="inlineStr">
+        <is>
+          <t>85.49</t>
+        </is>
+      </c>
+      <c r="CR18" t="inlineStr">
+        <is>
+          <t>89.58</t>
+        </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
@@ -18362,7 +18430,7 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
@@ -18377,22 +18445,22 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -18587,11 +18655,15 @@
           <t>82.66</t>
         </is>
       </c>
-      <c r="CQ19" t="n">
-        <v>85.83</v>
-      </c>
-      <c r="CR19" t="n">
-        <v>89.95</v>
+      <c r="CQ19" t="inlineStr">
+        <is>
+          <t>85.83</t>
+        </is>
+      </c>
+      <c r="CR19" t="inlineStr">
+        <is>
+          <t>89.95</t>
+        </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
